--- a/Phase 2/assignment_results.xlsx
+++ b/Phase 2/assignment_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dar\Project\CP-SAT-Test\Phase 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBC5522-93C0-4953-9394-72D187C5B6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078DF70A-B8BB-4709-BA9D-7AC7B80D4B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88371,5 +88371,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>